--- a/public/designer-data/manual_playtest_builds.xlsx
+++ b/public/designer-data/manual_playtest_builds.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,6 +439,9 @@
       <c r="M1" t="str">
         <v>enabled</v>
       </c>
+      <c r="N1" t="str">
+        <v>classId</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -480,6 +483,9 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -521,6 +527,9 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -562,6 +571,9 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -603,6 +615,9 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -644,6 +659,9 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -685,6 +703,9 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -726,6 +747,9 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -767,6 +791,9 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -808,6 +835,9 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -849,6 +879,9 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -890,6 +923,9 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -931,6 +967,9 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -972,6 +1011,9 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1013,6 +1055,9 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1054,6 +1099,9 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1095,6 +1143,9 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1136,6 +1187,9 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="str">
+        <v>warrior_t</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1177,10 +1231,409 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="str">
+        <v>warrior_t</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Challenge-1</v>
+      </c>
+      <c r="B20" t="str">
+        <v>CH-1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>鱼人登陆队</v>
+      </c>
+      <c r="D20" t="str">
+        <v>balance</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Challenge-2</v>
+      </c>
+      <c r="B21" t="str">
+        <v>CH-2</v>
+      </c>
+      <c r="C21" t="str">
+        <v>烛火与潮汐</v>
+      </c>
+      <c r="D21" t="str">
+        <v>balance</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Challenge-3</v>
+      </c>
+      <c r="B22" t="str">
+        <v>CH-3</v>
+      </c>
+      <c r="C22" t="str">
+        <v>老瞎眼演练</v>
+      </c>
+      <c r="D22" t="str">
+        <v>expert</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>WestFall-1</v>
+      </c>
+      <c r="B23" t="str">
+        <v>WF-1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>南瓜农场</v>
+      </c>
+      <c r="D23" t="str">
+        <v>easy</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>WestFall-2</v>
+      </c>
+      <c r="B24" t="str">
+        <v>WF-2</v>
+      </c>
+      <c r="C24" t="str">
+        <v>哨兵岭</v>
+      </c>
+      <c r="D24" t="str">
+        <v>balance</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>WestFall-3</v>
+      </c>
+      <c r="B25" t="str">
+        <v>WF-3</v>
+      </c>
+      <c r="C25" t="str">
+        <v>月溪镇</v>
+      </c>
+      <c r="D25" t="str">
+        <v>balance</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>WestFall-4</v>
+      </c>
+      <c r="B26" t="str">
+        <v>WF-4</v>
+      </c>
+      <c r="C26" t="str">
+        <v>死亡矿井</v>
+      </c>
+      <c r="D26" t="str">
+        <v>expert</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>WestFall-5</v>
+      </c>
+      <c r="B27" t="str">
+        <v>WF-5</v>
+      </c>
+      <c r="C27" t="str">
+        <v>灯塔</v>
+      </c>
+      <c r="D27" t="str">
+        <v>hard</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>manual_user_2026-07-26</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>manual_playtest_difficulty</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="str">
+        <v>druid_bear_t</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>WestFall-6</v>
+      </c>
+      <c r="B28" t="str">
+        <v>WF-6</v>
+      </c>
+      <c r="C28" t="str">
+        <v>海岸</v>
+      </c>
+      <c r="D28" t="str">
+        <v>expert</v>
+      </c>
+      <c r="E28" t="str">
+        <v>裂伤,痛击,月火术,铁鬃,树皮术,沉睡者之怒,低吼</v>
+      </c>
+      <c r="F28" t="str">
+        <v>druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_moonfire,druid_bear_t_ironfur,druid_bear_t_barkskin,druid_bear_t_rage_of_the_sleeper,druid_bear_t_growl</v>
+      </c>
+      <c r="G28" t="str">
+        <v>野性专注,疼痛豁免,铁棘</v>
+      </c>
+      <c r="H28" t="str">
+        <v>druid_bear_t_savage_focus,druid_bear_t_pain_immunity,druid_bear_t_iron_thorns</v>
+      </c>
+      <c r="I28" t="str">
+        <v>manual_user_2026-07-29</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>manual_playtest_result_and_recommended_build</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="str">
+        <v>druid_bear_t</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N28"/>
   </ignoredErrors>
 </worksheet>
 </file>